--- a/data/processed/positivacao/2022-11_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-11_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25413,7 +25413,7 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B965" t="inlineStr"/>
@@ -36869,7 +36869,7 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr"/>
@@ -66021,7 +66021,7 @@
     <row r="2528">
       <c r="A2528" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2528" t="inlineStr"/>
@@ -67692,12 +67692,12 @@
       <c r="A2593" t="inlineStr"/>
       <c r="B2593" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 13 cliente(s), não positivou 90 cliente(s) - Total vendido: R$ 37.334,88
+          <t>Vendedor 1 - VENDEDOR 01: positivou 13 cliente(s), não positivou 90 cliente(s) - Total vendido: R$ 37.334,88
 Vendedor 18 - LOJA: positivou 120 cliente(s), não positivou 732 cliente(s) - Total vendido: R$ 90.476,42
-Vendedor 3 - FERNANDA: positivou 107 cliente(s), não positivou 333 cliente(s) - Total vendido: R$ 156.866,29
-Vendedor 4 - DANIELA: positivou 60 cliente(s), não positivou 610 cliente(s) - Total vendido: R$ 35.469,90
+Vendedor 3 - VENDEDOR 03: positivou 107 cliente(s), não positivou 333 cliente(s) - Total vendido: R$ 156.866,29
+Vendedor 4 - VENDEDOR 04: positivou 60 cliente(s), não positivou 610 cliente(s) - Total vendido: R$ 35.469,90
 Vendedor 5 - SITE: positivou 9 cliente(s), não positivou 441 cliente(s) - Total vendido: R$ 835,77
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2593" t="inlineStr"/>
